--- a/CSL_Computer_Lab_Logs.xlsx
+++ b/CSL_Computer_Lab_Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EAE1339-40CC-4A5D-A732-E054C75734A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62077524-AFBC-402C-86FD-4DEEBE064021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A7044856-98E4-413E-9204-68376B922791}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A7044856-98E4-413E-9204-68376B922791}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="81">
   <si>
     <t xml:space="preserve">ID Number </t>
   </si>
@@ -211,6 +208,75 @@
   </si>
   <si>
     <t>Tuesday March 31, 2026</t>
+  </si>
+  <si>
+    <t>Wednesday April 1, 2026</t>
+  </si>
+  <si>
+    <t>Thursday April 2, 2026</t>
+  </si>
+  <si>
+    <t>Tuesday April 7, 2026</t>
+  </si>
+  <si>
+    <t>Wednesday April 8, 2026</t>
+  </si>
+  <si>
+    <t>Thursday April 9, 2026</t>
+  </si>
+  <si>
+    <t>Alicia Williams</t>
+  </si>
+  <si>
+    <t>Friday April 10, 2026</t>
+  </si>
+  <si>
+    <t>Monday April 13, 2026</t>
+  </si>
+  <si>
+    <t>A. Powell</t>
+  </si>
+  <si>
+    <t>Tuesday April 14, 2026</t>
+  </si>
+  <si>
+    <t>Joseph HoLung</t>
+  </si>
+  <si>
+    <t>Thursday April 16, 2026</t>
+  </si>
+  <si>
+    <t>Friday April 17, 2026</t>
+  </si>
+  <si>
+    <t>Monday April 20, 2026</t>
+  </si>
+  <si>
+    <t>Wednesday April 22, 2026</t>
+  </si>
+  <si>
+    <t>Thursday April 23, 2026</t>
+  </si>
+  <si>
+    <t>Friday April 24, 2026</t>
+  </si>
+  <si>
+    <t>Monday April 27, 2026</t>
+  </si>
+  <si>
+    <t>Wednesday April 29, 2026</t>
+  </si>
+  <si>
+    <t>Friday May 1, 2026</t>
+  </si>
+  <si>
+    <t>6201747-1</t>
+  </si>
+  <si>
+    <t>Tuesday May 5, 2026</t>
+  </si>
+  <si>
+    <t>Wednesday May 6, 2026</t>
   </si>
 </sst>
 </file>
@@ -389,9 +455,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -429,7 +495,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -535,7 +601,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -677,7 +743,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -685,7 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14A9A53-A167-4C1B-B6D1-AF4911C9B400}">
-  <dimension ref="A1:C1698"/>
+  <dimension ref="A1:C1987"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -18647,17 +18713,2947 @@
         <v>3</v>
       </c>
     </row>
+    <row r="1700" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1700" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1700" s="7"/>
+      <c r="C1700" s="7"/>
+    </row>
+    <row r="1701" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1701" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1701" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1701" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1702" s="3">
+        <v>620173353</v>
+      </c>
+      <c r="B1702" s="4">
+        <v>0.3576388888888889</v>
+      </c>
+      <c r="C1702" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1703" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1703" s="4">
+        <v>0.35902777777777778</v>
+      </c>
+      <c r="C1703" s="4">
+        <v>0.73750000000000004</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1704" s="3">
+        <v>620179780</v>
+      </c>
+      <c r="B1704" s="4">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="C1704" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1705" s="3">
+        <v>620180210</v>
+      </c>
+      <c r="B1705" s="4">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="C1705" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1706" s="3">
+        <v>620179063</v>
+      </c>
+      <c r="B1706" s="4">
+        <v>0.36944444444444446</v>
+      </c>
+      <c r="C1706" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1707" s="3">
+        <v>620181072</v>
+      </c>
+      <c r="B1707" s="4">
+        <v>0.38472222222222224</v>
+      </c>
+      <c r="C1707" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1708" s="3">
+        <v>620177230</v>
+      </c>
+      <c r="B1708" s="4">
+        <v>0.42152777777777778</v>
+      </c>
+      <c r="C1708" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1709" s="3">
+        <v>620134472</v>
+      </c>
+      <c r="B1709" s="4">
+        <v>0.42708333333333331</v>
+      </c>
+      <c r="C1709" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1710" s="3">
+        <v>620181049</v>
+      </c>
+      <c r="B1710" s="4">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="C1710" s="4">
+        <v>0.5708333333333333</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1711" s="3">
+        <v>620183385</v>
+      </c>
+      <c r="B1711" s="4">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="C1711" s="4">
+        <v>0.56805555555555554</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1712" s="3">
+        <v>620155108</v>
+      </c>
+      <c r="B1712" s="4">
+        <v>0.46041666666666664</v>
+      </c>
+      <c r="C1712" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1713" s="3">
+        <v>620178040</v>
+      </c>
+      <c r="B1713" s="4">
+        <v>0.46180555555555558</v>
+      </c>
+      <c r="C1713" s="4">
+        <v>0.58194444444444449</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1714" s="3">
+        <v>620140651</v>
+      </c>
+      <c r="B1714" s="4">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C1714" s="4">
+        <v>0.49791666666666667</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1715" s="3">
+        <v>620182371</v>
+      </c>
+      <c r="B1715" s="4">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C1715" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1716" s="3">
+        <v>620157657</v>
+      </c>
+      <c r="B1716" s="4">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="C1716" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1717" s="3">
+        <v>620169951</v>
+      </c>
+      <c r="B1717" s="4">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="C1717" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1718" s="3">
+        <v>620169176</v>
+      </c>
+      <c r="B1718" s="4">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="C1718" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1719" s="3">
+        <v>620179901</v>
+      </c>
+      <c r="B1719" s="4">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="C1719" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1720" s="3">
+        <v>620165627</v>
+      </c>
+      <c r="B1720" s="4">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="C1720" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1721" s="3">
+        <v>620184863</v>
+      </c>
+      <c r="B1721" s="4">
+        <v>0.52152777777777781</v>
+      </c>
+      <c r="C1721" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1722" s="3">
+        <v>620171104</v>
+      </c>
+      <c r="B1722" s="4">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="C1722" s="4">
+        <v>0.70694444444444449</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1723" s="3">
+        <v>620171889</v>
+      </c>
+      <c r="B1723" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C1723" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1724" s="3">
+        <v>620180253</v>
+      </c>
+      <c r="B1724" s="4">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="C1724" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1725" s="3">
+        <v>620118097</v>
+      </c>
+      <c r="B1725" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="C1725" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1726" s="3">
+        <v>620185007</v>
+      </c>
+      <c r="B1726" s="4">
+        <v>0.65208333333333335</v>
+      </c>
+      <c r="C1726" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1727" s="3">
+        <v>620177441</v>
+      </c>
+      <c r="B1727" s="4">
+        <v>0.64513888888888893</v>
+      </c>
+      <c r="C1727" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1728" s="3">
+        <v>620172242</v>
+      </c>
+      <c r="B1728" s="4">
+        <v>0.69513888888888886</v>
+      </c>
+      <c r="C1728" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1729" s="3">
+        <v>620173189</v>
+      </c>
+      <c r="B1729" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1729" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1731" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1731" s="7"/>
+      <c r="C1731" s="7"/>
+    </row>
+    <row r="1732" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1732" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1732" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1732" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1733" s="3">
+        <v>620178735</v>
+      </c>
+      <c r="B1733" s="4">
+        <v>0.35347222222222224</v>
+      </c>
+      <c r="C1733" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1734" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1734" s="4">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="C1734" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1735" s="3">
+        <v>620147797</v>
+      </c>
+      <c r="B1735" s="4">
+        <v>0.37708333333333333</v>
+      </c>
+      <c r="C1735" s="4">
+        <v>0.68194444444444446</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1736" s="3">
+        <v>620134472</v>
+      </c>
+      <c r="B1736" s="4">
+        <v>0.39861111111111114</v>
+      </c>
+      <c r="C1736" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1737" s="3">
+        <v>620171306</v>
+      </c>
+      <c r="B1737" s="4">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="C1737" s="4">
+        <v>0.55208333333333337</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1738" s="3">
+        <v>620179228</v>
+      </c>
+      <c r="B1738" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="C1738" s="4">
+        <v>0.49166666666666664</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1739" s="3">
+        <v>620156193</v>
+      </c>
+      <c r="B1739" s="4">
+        <v>0.42777777777777776</v>
+      </c>
+      <c r="C1739" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1740" s="3">
+        <v>620179073</v>
+      </c>
+      <c r="B1740" s="4">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="C1740" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1741" s="3">
+        <v>620171195</v>
+      </c>
+      <c r="B1741" s="4">
+        <v>0.49375000000000002</v>
+      </c>
+      <c r="C1741" s="4">
+        <v>0.55486111111111114</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1742" s="3">
+        <v>620168300</v>
+      </c>
+      <c r="B1742" s="4">
+        <v>0.51458333333333328</v>
+      </c>
+      <c r="C1742" s="4">
+        <v>0.62847222222222221</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1743" s="3">
+        <v>620177596</v>
+      </c>
+      <c r="B1743" s="4">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="C1743" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1744" s="3">
+        <v>620156105</v>
+      </c>
+      <c r="B1744" s="4">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C1744" s="4">
+        <v>0.68194444444444446</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1745" s="3">
+        <v>620161749</v>
+      </c>
+      <c r="B1745" s="4">
+        <v>0.5854166666666667</v>
+      </c>
+      <c r="C1745" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1746" s="3">
+        <v>620181097</v>
+      </c>
+      <c r="B1746" s="4">
+        <v>0.47847222222222224</v>
+      </c>
+      <c r="C1746" s="4">
+        <v>0.48888888888888887</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1748" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1748" s="7"/>
+      <c r="C1748" s="7"/>
+    </row>
+    <row r="1749" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1749" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1749" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1749" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1750" s="3">
+        <v>620134472</v>
+      </c>
+      <c r="B1750" s="4">
+        <v>0.31111111111111112</v>
+      </c>
+      <c r="C1750" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1751" s="3">
+        <v>620178735</v>
+      </c>
+      <c r="B1751" s="4">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="C1751" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1752" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1752" s="4">
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="C1752" s="4">
+        <v>0.64166666666666672</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1753" s="3">
+        <v>620164549</v>
+      </c>
+      <c r="B1753" s="4">
+        <v>0.41805555555555557</v>
+      </c>
+      <c r="C1753" s="4">
+        <v>0.69791666666666663</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1754" s="3">
+        <v>620179260</v>
+      </c>
+      <c r="B1754" s="4">
+        <v>0.44236111111111109</v>
+      </c>
+      <c r="C1754" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1755" s="3">
+        <v>620180210</v>
+      </c>
+      <c r="B1755" s="4">
+        <v>0.45208333333333334</v>
+      </c>
+      <c r="C1755" s="4">
+        <v>0.49861111111111112</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1756" s="3">
+        <v>620126076</v>
+      </c>
+      <c r="B1756" s="4">
+        <v>0.45902777777777776</v>
+      </c>
+      <c r="C1756" s="4">
+        <v>0.49722222222222223</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1757" s="3">
+        <v>620179470</v>
+      </c>
+      <c r="B1757" s="4">
+        <v>0.4597222222222222</v>
+      </c>
+      <c r="C1757" s="4">
+        <v>0.50138888888888888</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1758" s="3">
+        <v>620157657</v>
+      </c>
+      <c r="B1758" s="4">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="C1758" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1759" s="3">
+        <v>620161749</v>
+      </c>
+      <c r="B1759" s="4">
+        <v>0.51527777777777772</v>
+      </c>
+      <c r="C1759" s="4">
+        <v>0.6430555555555556</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1760" s="3">
+        <v>620151976</v>
+      </c>
+      <c r="B1760" s="4">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="C1760" s="4">
+        <v>0.58611111111111114</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1761" s="3">
+        <v>620154978</v>
+      </c>
+      <c r="B1761" s="4">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="C1761" s="4">
+        <v>0.59097222222222223</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1762" s="3">
+        <v>620163399</v>
+      </c>
+      <c r="B1762" s="4">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="C1762" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1763" s="3">
+        <v>620169951</v>
+      </c>
+      <c r="B1763" s="4">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C1763" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1764" s="3">
+        <v>620175368</v>
+      </c>
+      <c r="B1764" s="4">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C1764" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1765" s="3">
+        <v>620179901</v>
+      </c>
+      <c r="B1765" s="4">
+        <v>0.64722222222222225</v>
+      </c>
+      <c r="C1765" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1766" s="3">
+        <v>620154978</v>
+      </c>
+      <c r="B1766" s="4">
+        <v>0.65138888888888891</v>
+      </c>
+      <c r="C1766" s="4">
+        <v>0.68402777777777779</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1767" s="3">
+        <v>620170120</v>
+      </c>
+      <c r="B1767" s="4">
+        <v>0.75347222222222221</v>
+      </c>
+      <c r="C1767" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1769" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1769" s="7"/>
+      <c r="C1769" s="7"/>
+    </row>
+    <row r="1770" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1770" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1770" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1770" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1771" s="3">
+        <v>620178735</v>
+      </c>
+      <c r="B1771" s="4">
+        <v>0.34930555555555554</v>
+      </c>
+      <c r="C1771" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1772" s="3">
+        <v>620184863</v>
+      </c>
+      <c r="B1772" s="4">
+        <v>0.35486111111111113</v>
+      </c>
+      <c r="C1772" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1773" s="3">
+        <v>620181049</v>
+      </c>
+      <c r="B1773" s="4">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="C1773" s="4">
+        <v>0.5131944444444444</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1774" s="3">
+        <v>620165627</v>
+      </c>
+      <c r="B1774" s="4">
+        <v>0.45347222222222222</v>
+      </c>
+      <c r="C1774" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1775" s="3">
+        <v>620180932</v>
+      </c>
+      <c r="B1775" s="4">
+        <v>0.4909722222222222</v>
+      </c>
+      <c r="C1775" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1776" s="3">
+        <v>620181440</v>
+      </c>
+      <c r="B1776" s="4">
+        <v>0.49861111111111112</v>
+      </c>
+      <c r="C1776" s="4">
+        <v>0.54513888888888884</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1777" s="3">
+        <v>620173138</v>
+      </c>
+      <c r="B1777" s="4">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="C1777" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1778" s="3">
+        <v>620154255</v>
+      </c>
+      <c r="B1778" s="4">
+        <v>0.54374999999999996</v>
+      </c>
+      <c r="C1778" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1779" s="3">
+        <v>620171889</v>
+      </c>
+      <c r="B1779" s="4">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C1779" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1780" s="3">
+        <v>620179063</v>
+      </c>
+      <c r="B1780" s="4">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C1780" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1781" s="3">
+        <v>620133373</v>
+      </c>
+      <c r="B1781" s="4">
+        <v>0.72986111111111107</v>
+      </c>
+      <c r="C1781" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1783" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1783" s="7"/>
+      <c r="C1783" s="7"/>
+    </row>
+    <row r="1784" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1784" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1784" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1784" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1785" s="3">
+        <v>620150096</v>
+      </c>
+      <c r="B1785" s="4">
+        <v>0.38958333333333334</v>
+      </c>
+      <c r="C1785" s="4">
+        <v>0.41180555555555554</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1786" s="3">
+        <v>620173353</v>
+      </c>
+      <c r="B1786" s="4">
+        <v>0.39027777777777778</v>
+      </c>
+      <c r="C1786" s="4">
+        <v>0.69513888888888886</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1787" s="3">
+        <v>620177606</v>
+      </c>
+      <c r="B1787" s="4">
+        <v>0.40069444444444446</v>
+      </c>
+      <c r="C1787" s="4">
+        <v>0.4152777777777778</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1788" s="3">
+        <v>620179724</v>
+      </c>
+      <c r="B1788" s="4">
+        <v>0.40138888888888891</v>
+      </c>
+      <c r="C1788" s="4">
+        <v>0.4152777777777778</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1789" s="3">
+        <v>620178735</v>
+      </c>
+      <c r="B1789" s="4">
+        <v>0.40416666666666667</v>
+      </c>
+      <c r="C1789" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1790" s="3">
+        <v>620171308</v>
+      </c>
+      <c r="B1790" s="4">
+        <v>0.40625</v>
+      </c>
+      <c r="C1790" s="4">
+        <v>0.50624999999999998</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1791" s="3">
+        <v>620184863</v>
+      </c>
+      <c r="B1791" s="4">
+        <v>0.41875000000000001</v>
+      </c>
+      <c r="C1791" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1792" s="3">
+        <v>620178511</v>
+      </c>
+      <c r="B1792" s="4">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="C1792" s="4">
+        <v>0.53333333333333333</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1793" s="3">
+        <v>620185024</v>
+      </c>
+      <c r="B1793" s="4">
+        <v>0.45347222222222222</v>
+      </c>
+      <c r="C1793" s="4">
+        <v>0.65486111111111112</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1794" s="3">
+        <v>620179995</v>
+      </c>
+      <c r="B1794" s="4">
+        <v>0.50347222222222221</v>
+      </c>
+      <c r="C1794" s="4">
+        <v>0.75972222222222219</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1795" s="3">
+        <v>620180649</v>
+      </c>
+      <c r="B1795" s="4">
+        <v>0.49652777777777779</v>
+      </c>
+      <c r="C1795" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1796" s="3">
+        <v>620154684</v>
+      </c>
+      <c r="B1796" s="4">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C1796" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1797" s="3">
+        <v>620147417</v>
+      </c>
+      <c r="B1797" s="4">
+        <v>0.51041666666666663</v>
+      </c>
+      <c r="C1797" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1798" s="3">
+        <v>620178591</v>
+      </c>
+      <c r="B1798" s="4">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C1798" s="4">
+        <v>0.56944444444444442</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1799" s="3">
+        <v>620165625</v>
+      </c>
+      <c r="B1799" s="4">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="C1799" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1800" s="3">
+        <v>620182505</v>
+      </c>
+      <c r="B1800" s="4">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C1800" s="4">
+        <v>0.57708333333333328</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1801" s="3">
+        <v>620180648</v>
+      </c>
+      <c r="B1801" s="4">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C1801" s="4">
+        <v>0.62638888888888888</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1802" s="3">
+        <v>620178511</v>
+      </c>
+      <c r="B1802" s="4">
+        <v>0.57847222222222228</v>
+      </c>
+      <c r="C1802" s="4">
+        <v>0.61944444444444446</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1803" s="3">
+        <v>620148743</v>
+      </c>
+      <c r="B1803" s="4">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="C1803" s="4">
+        <v>0.65416666666666667</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1804" s="3">
+        <v>620181836</v>
+      </c>
+      <c r="B1804" s="4">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="C1804" s="4">
+        <v>0.65416666666666667</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1805" s="3">
+        <v>620176146</v>
+      </c>
+      <c r="B1805" s="4">
+        <v>0.59375</v>
+      </c>
+      <c r="C1805" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1806" s="3">
+        <v>620172759</v>
+      </c>
+      <c r="B1806" s="4">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="C1806" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1807" s="3">
+        <v>620147657</v>
+      </c>
+      <c r="B1807" s="4">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="C1807" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1808" s="3">
+        <v>620173092</v>
+      </c>
+      <c r="B1808" s="4">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="C1808" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1809" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1809" s="4">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="C1809" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1810" s="3">
+        <v>620165681</v>
+      </c>
+      <c r="B1810" s="4">
+        <v>0.6118055555555556</v>
+      </c>
+      <c r="C1810" s="4">
+        <v>0.62152777777777779</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1811" s="3">
+        <v>620183706</v>
+      </c>
+      <c r="B1811" s="4">
+        <v>0.64236111111111116</v>
+      </c>
+      <c r="C1811" s="4">
+        <v>0.75902777777777775</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1812" s="3">
+        <v>620180230</v>
+      </c>
+      <c r="B1812" s="4">
+        <v>0.68333333333333335</v>
+      </c>
+      <c r="C1812" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1813" s="3">
+        <v>620156578</v>
+      </c>
+      <c r="B1813" s="4">
+        <v>0.72638888888888886</v>
+      </c>
+      <c r="C1813" s="4">
+        <v>0.78333333333333333</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1814" s="3">
+        <v>620146618</v>
+      </c>
+      <c r="B1814" s="4">
+        <v>0.73124999999999996</v>
+      </c>
+      <c r="C1814" s="4">
+        <v>0.78333333333333333</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1816" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1816" s="7"/>
+      <c r="C1816" s="7"/>
+    </row>
+    <row r="1817" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1817" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1817" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1817" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1818" s="3">
+        <v>620181049</v>
+      </c>
+      <c r="B1818" s="4">
+        <v>0.38124999999999998</v>
+      </c>
+      <c r="C1818" s="4">
+        <v>0.46319444444444446</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1819" s="3">
+        <v>620178735</v>
+      </c>
+      <c r="B1819" s="4">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C1819" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1820" s="3">
+        <v>620178860</v>
+      </c>
+      <c r="B1820" s="4">
+        <v>0.40625</v>
+      </c>
+      <c r="C1820" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1821" s="3">
+        <v>620178311</v>
+      </c>
+      <c r="B1821" s="4">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="C1821" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1822" s="3">
+        <v>620174538</v>
+      </c>
+      <c r="B1822" s="4">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="C1822" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1823" s="3">
+        <v>620184863</v>
+      </c>
+      <c r="B1823" s="4">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="C1823" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1824" s="3">
+        <v>620180736</v>
+      </c>
+      <c r="B1824" s="4">
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="C1824" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1825" s="3">
+        <v>620178511</v>
+      </c>
+      <c r="B1825" s="4">
+        <v>0.47083333333333333</v>
+      </c>
+      <c r="C1825" s="4">
+        <v>0.52777777777777779</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1826" s="3">
+        <v>620168300</v>
+      </c>
+      <c r="B1826" s="4">
+        <v>0.56111111111111112</v>
+      </c>
+      <c r="C1826" s="4">
+        <v>0.61250000000000004</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1827" s="3">
+        <v>620179901</v>
+      </c>
+      <c r="B1827" s="4">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C1827" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1828" s="3">
+        <v>620147777</v>
+      </c>
+      <c r="B1828" s="4">
+        <v>0.38263888888888886</v>
+      </c>
+      <c r="C1828" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1829" s="3">
+        <v>620162707</v>
+      </c>
+      <c r="B1829" s="4">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="C1829" s="4">
+        <v>0.65972222222222221</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1830" s="3">
+        <v>620160909</v>
+      </c>
+      <c r="B1830" s="4">
+        <v>0.57986111111111116</v>
+      </c>
+      <c r="C1830" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1831" s="3">
+        <v>620181049</v>
+      </c>
+      <c r="B1831" s="4">
+        <v>0.62291666666666667</v>
+      </c>
+      <c r="C1831" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1832" s="3">
+        <v>620163593</v>
+      </c>
+      <c r="B1832" s="4">
+        <v>0.66180555555555554</v>
+      </c>
+      <c r="C1832" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1833" s="3">
+        <v>620160612</v>
+      </c>
+      <c r="B1833" s="4">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="C1833" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1834" s="3">
+        <v>620157290</v>
+      </c>
+      <c r="B1834" s="4">
+        <v>0.66319444444444442</v>
+      </c>
+      <c r="C1834" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1835" s="3">
+        <v>620164679</v>
+      </c>
+      <c r="B1835" s="4">
+        <v>0.6645833333333333</v>
+      </c>
+      <c r="C1835" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1836" s="3">
+        <v>620179200</v>
+      </c>
+      <c r="B1836" s="4">
+        <v>0.66874999999999996</v>
+      </c>
+      <c r="C1836" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1837" s="3">
+        <v>620133873</v>
+      </c>
+      <c r="B1837" s="4">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C1837" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1838" s="3">
+        <v>620166353</v>
+      </c>
+      <c r="B1838" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="C1838" s="4">
+        <v>0.72291666666666665</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1840" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1840" s="7"/>
+      <c r="C1840" s="7"/>
+    </row>
+    <row r="1841" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1841" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1841" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1841" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1842" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1842" s="4">
+        <v>0.39027777777777778</v>
+      </c>
+      <c r="C1842" s="4">
+        <v>0.43402777777777779</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1843" s="3">
+        <v>620173353</v>
+      </c>
+      <c r="B1843" s="4">
+        <v>0.40833333333333333</v>
+      </c>
+      <c r="C1843" s="4">
+        <v>0.60138888888888886</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1844" s="3">
+        <v>620179296</v>
+      </c>
+      <c r="B1844" s="4">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="C1844" s="4">
+        <v>0.46805555555555556</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1845" s="3">
+        <v>620106262</v>
+      </c>
+      <c r="B1845" s="4">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="C1845" s="4">
+        <v>0.46805555555555556</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1846" s="3">
+        <v>620177311</v>
+      </c>
+      <c r="B1846" s="4">
+        <v>0.44305555555555554</v>
+      </c>
+      <c r="C1846" s="4">
+        <v>0.46805555555555556</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1847" s="3">
+        <v>620156105</v>
+      </c>
+      <c r="B1847" s="4">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="C1847" s="4">
+        <v>0.64444444444444449</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1848" s="3">
+        <v>620170109</v>
+      </c>
+      <c r="B1848" s="4">
+        <v>0.51597222222222228</v>
+      </c>
+      <c r="C1848" s="4">
+        <v>0.55833333333333335</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1849" s="3">
+        <v>620149857</v>
+      </c>
+      <c r="B1849" s="4">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="C1849" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1850" s="3">
+        <v>620170492</v>
+      </c>
+      <c r="B1850" s="4">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="C1850" s="4">
+        <v>0.65347222222222223</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1851" s="3">
+        <v>620177834</v>
+      </c>
+      <c r="B1851" s="4">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="C1851" s="4">
+        <v>0.65347222222222223</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1852" s="3">
+        <v>620171889</v>
+      </c>
+      <c r="B1852" s="4">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="C1852" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1853" s="3">
+        <v>620172759</v>
+      </c>
+      <c r="B1853" s="4">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C1853" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1854" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1854" s="4">
+        <v>0.61875000000000002</v>
+      </c>
+      <c r="C1854" s="4">
+        <v>0.65347222222222223</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1856" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1856" s="7"/>
+      <c r="C1856" s="7"/>
+    </row>
+    <row r="1857" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1857" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1857" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1857" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1858" s="3">
+        <v>620178715</v>
+      </c>
+      <c r="B1858" s="4">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C1858" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1859" s="3">
+        <v>620144870</v>
+      </c>
+      <c r="B1859" s="4">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C1859" s="4">
+        <v>0.51875000000000004</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1860" s="3">
+        <v>620171308</v>
+      </c>
+      <c r="B1860" s="4">
+        <v>0.41041666666666665</v>
+      </c>
+      <c r="C1860" s="4">
+        <v>0.43541666666666667</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1861" s="3">
+        <v>620172759</v>
+      </c>
+      <c r="B1861" s="4">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="C1861" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1862" s="3">
+        <v>620147657</v>
+      </c>
+      <c r="B1862" s="4">
+        <v>0.43819444444444444</v>
+      </c>
+      <c r="C1862" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1863" s="3">
+        <v>620146629</v>
+      </c>
+      <c r="B1863" s="4">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="C1863" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1864" s="3">
+        <v>620161749</v>
+      </c>
+      <c r="B1864" s="4">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="C1864" s="4">
+        <v>0.79236111111111107</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1865" s="3">
+        <v>620156103</v>
+      </c>
+      <c r="B1865" s="4">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="C1865" s="4">
+        <v>0.56111111111111112</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1866" s="3">
+        <v>620165627</v>
+      </c>
+      <c r="B1866" s="4">
+        <v>0.52569444444444446</v>
+      </c>
+      <c r="C1866" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1867" s="3">
+        <v>620163781</v>
+      </c>
+      <c r="B1867" s="4">
+        <v>0.59513888888888888</v>
+      </c>
+      <c r="C1867" s="4">
+        <v>0.63472222222222219</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1868" s="3">
+        <v>620171440</v>
+      </c>
+      <c r="B1868" s="4">
+        <v>0.69374999999999998</v>
+      </c>
+      <c r="C1868" s="4">
+        <v>0.75624999999999998</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1869" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1869" s="4">
+        <v>0.69374999999999998</v>
+      </c>
+      <c r="C1869" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1870" s="3">
+        <v>620182768</v>
+      </c>
+      <c r="B1870" s="4">
+        <v>0.69652777777777775</v>
+      </c>
+      <c r="C1870" s="4">
+        <v>0.70625000000000004</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1871" s="3">
+        <v>620148700</v>
+      </c>
+      <c r="B1871" s="4">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="C1871" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1872" s="3">
+        <v>620164296</v>
+      </c>
+      <c r="B1872" s="4">
+        <v>0.72847222222222219</v>
+      </c>
+      <c r="C1872" s="4">
+        <v>0.74722222222222223</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1873" s="3">
+        <v>620157892</v>
+      </c>
+      <c r="B1873" s="4">
+        <v>0.63611111111111107</v>
+      </c>
+      <c r="C1873" s="4">
+        <v>0.67500000000000004</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1874" s="3">
+        <v>620179260</v>
+      </c>
+      <c r="B1874" s="4">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="C1874" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1875" s="3">
+        <v>620161749</v>
+      </c>
+      <c r="B1875" s="4">
+        <v>0.71388888888888891</v>
+      </c>
+      <c r="C1875" s="4">
+        <v>0.80833333333333335</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1877" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1877" s="7"/>
+      <c r="C1877" s="7"/>
+    </row>
+    <row r="1878" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1878" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1878" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1878" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1879" s="3">
+        <v>620160648</v>
+      </c>
+      <c r="B1879" s="4">
+        <v>0.77013888888888893</v>
+      </c>
+      <c r="C1879" s="4">
+        <v>0.82916666666666672</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1880" s="3">
+        <v>620162443</v>
+      </c>
+      <c r="B1880" s="4">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C1880" s="4">
+        <v>0.82916666666666672</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1882" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1882" s="7"/>
+      <c r="C1882" s="7"/>
+    </row>
+    <row r="1883" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1883" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1883" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1883" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1884" s="3">
+        <v>620178496</v>
+      </c>
+      <c r="B1884" s="4">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C1884" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1886" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1886" s="7"/>
+      <c r="C1886" s="7"/>
+    </row>
+    <row r="1887" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1887" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1887" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1887" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1888" s="3">
+        <v>620179296</v>
+      </c>
+      <c r="B1888" s="4">
+        <v>0.44027777777777777</v>
+      </c>
+      <c r="C1888" s="4">
+        <v>0.51944444444444449</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1889" s="3">
+        <v>620162930</v>
+      </c>
+      <c r="B1889" s="4">
+        <v>0.44166666666666665</v>
+      </c>
+      <c r="C1889" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1890" s="3">
+        <v>620171195</v>
+      </c>
+      <c r="B1890" s="4">
+        <v>0.44374999999999998</v>
+      </c>
+      <c r="C1890" s="4">
+        <v>0.51180555555555551</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1891" s="3">
+        <v>620161166</v>
+      </c>
+      <c r="B1891" s="4">
+        <v>0.46805555555555556</v>
+      </c>
+      <c r="C1891" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1892" s="3">
+        <v>620179794</v>
+      </c>
+      <c r="B1892" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C1892" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1893" s="3">
+        <v>620169560</v>
+      </c>
+      <c r="B1893" s="4">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="C1893" s="4">
+        <v>0.64930555555555558</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1894" s="3">
+        <v>620171296</v>
+      </c>
+      <c r="B1894" s="4">
+        <v>0.51180555555555551</v>
+      </c>
+      <c r="C1894" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1895" s="3">
+        <v>620177077</v>
+      </c>
+      <c r="B1895" s="4">
+        <v>0.53541666666666665</v>
+      </c>
+      <c r="C1895" s="4">
+        <v>0.5854166666666667</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1896" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1896" s="4">
+        <v>0.56874999999999998</v>
+      </c>
+      <c r="C1896" s="4">
+        <v>0.64722222222222225</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1897" s="3">
+        <v>620183706</v>
+      </c>
+      <c r="B1897" s="4">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C1897" s="4">
+        <v>0.65486111111111112</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1898" s="3">
+        <v>620180649</v>
+      </c>
+      <c r="B1898" s="4">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C1898" s="4">
+        <v>0.65486111111111112</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1900" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1900" s="7"/>
+      <c r="C1900" s="7"/>
+    </row>
+    <row r="1901" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1901" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1901" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1901" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1902" s="3">
+        <v>620181112</v>
+      </c>
+      <c r="B1902" s="4">
+        <v>0.38263888888888886</v>
+      </c>
+      <c r="C1902" s="4">
+        <v>0.52222222222222225</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1903" s="3">
+        <v>620171308</v>
+      </c>
+      <c r="B1903" s="4">
+        <v>0.38611111111111113</v>
+      </c>
+      <c r="C1903" s="4">
+        <v>0.52708333333333335</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1904" s="3">
+        <v>620161166</v>
+      </c>
+      <c r="B1904" s="4">
+        <v>0.41111111111111109</v>
+      </c>
+      <c r="C1904" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1905" s="3">
+        <v>620156105</v>
+      </c>
+      <c r="B1905" s="4">
+        <v>0.50416666666666665</v>
+      </c>
+      <c r="C1905" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1906" s="3">
+        <v>620157657</v>
+      </c>
+      <c r="B1906" s="4">
+        <v>0.58472222222222225</v>
+      </c>
+      <c r="C1906" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1907" s="3">
+        <v>620177606</v>
+      </c>
+      <c r="B1907" s="4">
+        <v>0.63958333333333328</v>
+      </c>
+      <c r="C1907" s="4">
+        <v>0.67569444444444449</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1908" s="3">
+        <v>620160643</v>
+      </c>
+      <c r="B1908" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C1908" s="4">
+        <v>0.78541666666666665</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1909" s="3">
+        <v>620162443</v>
+      </c>
+      <c r="B1909" s="4">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="C1909" s="4">
+        <v>0.78819444444444442</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1911" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1911" s="7"/>
+      <c r="C1911" s="7"/>
+    </row>
+    <row r="1912" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1912" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1912" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1912" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1913" s="3">
+        <v>620150096</v>
+      </c>
+      <c r="B1913" s="4">
+        <v>0.32222222222222224</v>
+      </c>
+      <c r="C1913" s="4">
+        <v>0.37152777777777779</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1914" s="3">
+        <v>620179027</v>
+      </c>
+      <c r="B1914" s="4">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="C1914" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1916" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1916" s="7"/>
+      <c r="C1916" s="7"/>
+    </row>
+    <row r="1917" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1917" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1917" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1917" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1918" s="3">
+        <v>620163681</v>
+      </c>
+      <c r="B1918" s="4">
+        <v>0.30902777777777779</v>
+      </c>
+      <c r="C1918" s="4">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1919" s="3">
+        <v>620149119</v>
+      </c>
+      <c r="B1919" s="4">
+        <v>0.30902777777777779</v>
+      </c>
+      <c r="C1919" s="4">
+        <v>0.52777777777777779</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1920" s="3">
+        <v>620176040</v>
+      </c>
+      <c r="B1920" s="4">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="C1920" s="4">
+        <v>0.36527777777777776</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1921" s="3">
+        <v>620147578</v>
+      </c>
+      <c r="B1921" s="4">
+        <v>0.47152777777777777</v>
+      </c>
+      <c r="C1921" s="4">
+        <v>0.48055555555555557</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1922" s="3">
+        <v>620173022</v>
+      </c>
+      <c r="B1922" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C1922" s="4">
+        <v>0.52847222222222223</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1923" s="3">
+        <v>620159123</v>
+      </c>
+      <c r="B1923" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1923" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1924" s="3">
+        <v>620163394</v>
+      </c>
+      <c r="B1924" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1924" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1925" s="3">
+        <v>620172327</v>
+      </c>
+      <c r="B1925" s="4">
+        <v>0.42986111111111114</v>
+      </c>
+      <c r="C1925" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1927" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1927" s="7"/>
+      <c r="C1927" s="7"/>
+    </row>
+    <row r="1928" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1928" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1928" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1928" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1929" s="3">
+        <v>620147657</v>
+      </c>
+      <c r="B1929" s="4">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="C1929" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1930" s="3">
+        <v>620148700</v>
+      </c>
+      <c r="B1930" s="4">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="C1930" s="4">
+        <v>0.43958333333333333</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1931" s="3">
+        <v>620163646</v>
+      </c>
+      <c r="B1931" s="4">
+        <v>0.48541666666666666</v>
+      </c>
+      <c r="C1931" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1933" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1933" s="7"/>
+      <c r="C1933" s="7"/>
+    </row>
+    <row r="1934" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1934" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1934" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1934" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1935" s="3">
+        <v>620172677</v>
+      </c>
+      <c r="B1935" s="4">
+        <v>0.31736111111111109</v>
+      </c>
+      <c r="C1935" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1936" s="3">
+        <v>620171308</v>
+      </c>
+      <c r="B1936" s="4">
+        <v>0.38541666666666669</v>
+      </c>
+      <c r="C1936" s="4">
+        <v>0.54791666666666672</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1937" s="3">
+        <v>620132171</v>
+      </c>
+      <c r="B1937" s="4">
+        <v>0.40902777777777777</v>
+      </c>
+      <c r="C1937" s="4">
+        <v>0.42708333333333331</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1938" s="3">
+        <v>620137899</v>
+      </c>
+      <c r="B1938" s="4">
+        <v>0.42916666666666664</v>
+      </c>
+      <c r="C1938" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1939" s="3">
+        <v>620180644</v>
+      </c>
+      <c r="B1939" s="4">
+        <v>0.43263888888888891</v>
+      </c>
+      <c r="C1939" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1940" s="3">
+        <v>620183882</v>
+      </c>
+      <c r="B1940" s="4">
+        <v>0.47638888888888886</v>
+      </c>
+      <c r="C1940" s="4">
+        <v>0.54027777777777775</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1941" s="3">
+        <v>620132171</v>
+      </c>
+      <c r="B1941" s="4">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="C1941" s="4">
+        <v>0.62152777777777779</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1942" s="3">
+        <v>620172327</v>
+      </c>
+      <c r="B1942" s="4">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="C1942" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1943" s="3">
+        <v>620165631</v>
+      </c>
+      <c r="B1943" s="4">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="C1943" s="4">
+        <v>0.64583333333333337</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1944" s="3">
+        <v>620147403</v>
+      </c>
+      <c r="B1944" s="4">
+        <v>0.51666666666666672</v>
+      </c>
+      <c r="C1944" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1945" s="3">
+        <v>620178629</v>
+      </c>
+      <c r="B1945" s="4">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="C1945" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1946" s="3">
+        <v>620177752</v>
+      </c>
+      <c r="B1946" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C1946" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1947" s="3">
+        <v>620178328</v>
+      </c>
+      <c r="B1947" s="4">
+        <v>0.68263888888888891</v>
+      </c>
+      <c r="C1947" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1948" s="3">
+        <v>620165245</v>
+      </c>
+      <c r="B1948" s="4">
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="C1948" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1949" s="3">
+        <v>620148700</v>
+      </c>
+      <c r="B1949" s="4">
+        <v>0.71527777777777779</v>
+      </c>
+      <c r="C1949" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1951" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1951" s="7"/>
+      <c r="C1951" s="7"/>
+    </row>
+    <row r="1952" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1952" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1952" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1952" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1953" s="3">
+        <v>620178700</v>
+      </c>
+      <c r="B1953" s="4">
+        <v>0.3125</v>
+      </c>
+      <c r="C1953" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1954" s="3">
+        <v>620171296</v>
+      </c>
+      <c r="B1954" s="4">
+        <v>0.3215277777777778</v>
+      </c>
+      <c r="C1954" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1955" s="3">
+        <v>620173440</v>
+      </c>
+      <c r="B1955" s="4">
+        <v>0.32916666666666666</v>
+      </c>
+      <c r="C1955" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1956" s="3">
+        <v>620171724</v>
+      </c>
+      <c r="B1956" s="4">
+        <v>0.33958333333333335</v>
+      </c>
+      <c r="C1956" s="4">
+        <v>0.3576388888888889</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1957" s="3">
+        <v>620172434</v>
+      </c>
+      <c r="B1957" s="4">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="C1957" s="4">
+        <v>0.3576388888888889</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1958" s="3">
+        <v>620173877</v>
+      </c>
+      <c r="B1958" s="4">
+        <v>0.40763888888888888</v>
+      </c>
+      <c r="C1958" s="4">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1959" s="3">
+        <v>620181328</v>
+      </c>
+      <c r="B1959" s="4">
+        <v>0.40763888888888888</v>
+      </c>
+      <c r="C1959" s="4">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1960" s="3">
+        <v>620146580</v>
+      </c>
+      <c r="B1960" s="4">
+        <v>0.46736111111111112</v>
+      </c>
+      <c r="C1960" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1961" s="3">
+        <v>6201806409</v>
+      </c>
+      <c r="B1961" s="4">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="C1961" s="4">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1962" s="3">
+        <v>620183706</v>
+      </c>
+      <c r="B1962" s="4">
+        <v>0.49583333333333335</v>
+      </c>
+      <c r="C1962" s="4">
+        <v>0.53125</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1963" s="3">
+        <v>620149119</v>
+      </c>
+      <c r="B1963" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C1963" s="4">
+        <v>0.53472222222222221</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1964" s="3">
+        <v>620177242</v>
+      </c>
+      <c r="B1964" s="4">
+        <v>0.53055555555555556</v>
+      </c>
+      <c r="C1964" s="4">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1965" s="3">
+        <v>620163399</v>
+      </c>
+      <c r="B1965" s="4">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="C1965" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1966" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1966" s="4">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="C1966" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1968" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1968" s="7"/>
+      <c r="C1968" s="7"/>
+    </row>
+    <row r="1969" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1969" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1969" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1969" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1970" s="3">
+        <v>620128363</v>
+      </c>
+      <c r="B1970" s="4">
+        <v>0.31874999999999998</v>
+      </c>
+      <c r="C1970" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1971" s="3">
+        <v>620161166</v>
+      </c>
+      <c r="B1971" s="4">
+        <v>0.36388888888888887</v>
+      </c>
+      <c r="C1971" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1972" s="3">
+        <v>620165248</v>
+      </c>
+      <c r="B1972" s="4">
+        <v>0.43611111111111112</v>
+      </c>
+      <c r="C1972" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1973" s="3">
+        <v>620155024</v>
+      </c>
+      <c r="B1973" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="C1973" s="4">
+        <v>0.5805555555555556</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1974" s="3">
+        <v>620178918</v>
+      </c>
+      <c r="B1974" s="4">
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="C1974" s="4">
+        <v>0.53819444444444442</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1975" s="3">
+        <v>620180737</v>
+      </c>
+      <c r="B1975" s="4">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="C1975" s="4">
+        <v>0.65625</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1976" s="3">
+        <v>620171527</v>
+      </c>
+      <c r="B1976" s="4">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="C1976" s="4">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1977" s="3">
+        <v>620172338</v>
+      </c>
+      <c r="B1977" s="4">
+        <v>0.25624999999999998</v>
+      </c>
+      <c r="C1977" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1978" s="3">
+        <v>620164061</v>
+      </c>
+      <c r="B1978" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C1978" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1979" s="3">
+        <v>620149759</v>
+      </c>
+      <c r="B1979" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C1979" s="4">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1981" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1981" s="7"/>
+      <c r="C1981" s="7"/>
+    </row>
+    <row r="1982" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1982" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1982" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1982" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1983" s="3">
+        <v>620149759</v>
+      </c>
+      <c r="B1983" s="4">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C1983" s="4">
+        <v>0.57638888888888884</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1984" s="3">
+        <v>620176026</v>
+      </c>
+      <c r="B1984" s="4">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="C1984" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1985" s="3">
+        <v>620171195</v>
+      </c>
+      <c r="B1985" s="4">
+        <v>0.61319444444444449</v>
+      </c>
+      <c r="C1985" s="4">
+        <v>0.62222222222222223</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1986" s="3">
+        <v>620187519</v>
+      </c>
+      <c r="B1986" s="4">
+        <v>0.59305555555555556</v>
+      </c>
+      <c r="C1986" s="4">
+        <v>0.62638888888888888</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1987" s="3">
+        <v>620156207</v>
+      </c>
+      <c r="B1987" s="4">
+        <v>0.62986111111111109</v>
+      </c>
+      <c r="C1987" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="A1559:C1559"/>
-    <mergeCell ref="A1576:C1576"/>
-    <mergeCell ref="A1625:C1625"/>
-    <mergeCell ref="A1647:C1647"/>
-    <mergeCell ref="A1432:C1432"/>
-    <mergeCell ref="A1460:C1460"/>
-    <mergeCell ref="A1477:C1477"/>
-    <mergeCell ref="A1492:C1492"/>
-    <mergeCell ref="A1525:C1525"/>
+  <mergeCells count="69">
+    <mergeCell ref="A1933:C1933"/>
+    <mergeCell ref="A1951:C1951"/>
+    <mergeCell ref="A1968:C1968"/>
+    <mergeCell ref="A1981:C1981"/>
+    <mergeCell ref="A1886:C1886"/>
+    <mergeCell ref="A1900:C1900"/>
+    <mergeCell ref="A1911:C1911"/>
+    <mergeCell ref="A1916:C1916"/>
+    <mergeCell ref="A1927:C1927"/>
+    <mergeCell ref="A1816:C1816"/>
+    <mergeCell ref="A1840:C1840"/>
+    <mergeCell ref="A1856:C1856"/>
+    <mergeCell ref="A1877:C1877"/>
+    <mergeCell ref="A1882:C1882"/>
+    <mergeCell ref="A1700:C1700"/>
+    <mergeCell ref="A1731:C1731"/>
+    <mergeCell ref="A1748:C1748"/>
+    <mergeCell ref="A1769:C1769"/>
+    <mergeCell ref="A1783:C1783"/>
+    <mergeCell ref="A1259:C1259"/>
+    <mergeCell ref="A1288:C1288"/>
+    <mergeCell ref="A1339:C1339"/>
+    <mergeCell ref="A1365:C1365"/>
+    <mergeCell ref="A1400:C1400"/>
+    <mergeCell ref="A278:C278"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A271:C271"/>
+    <mergeCell ref="A229:C229"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A183:C183"/>
+    <mergeCell ref="A667:C667"/>
+    <mergeCell ref="A708:C708"/>
+    <mergeCell ref="A305:C305"/>
+    <mergeCell ref="A550:C550"/>
+    <mergeCell ref="A592:C592"/>
+    <mergeCell ref="A334:C334"/>
+    <mergeCell ref="A379:C379"/>
+    <mergeCell ref="A439:C439"/>
+    <mergeCell ref="A483:C483"/>
+    <mergeCell ref="A518:C518"/>
     <mergeCell ref="A743:C743"/>
     <mergeCell ref="A1141:C1141"/>
     <mergeCell ref="A1164:C1164"/>
@@ -18673,32 +21669,15 @@
     <mergeCell ref="A918:C918"/>
     <mergeCell ref="A955:C955"/>
     <mergeCell ref="A977:C977"/>
-    <mergeCell ref="A667:C667"/>
-    <mergeCell ref="A708:C708"/>
-    <mergeCell ref="A305:C305"/>
-    <mergeCell ref="A550:C550"/>
-    <mergeCell ref="A592:C592"/>
-    <mergeCell ref="A334:C334"/>
-    <mergeCell ref="A379:C379"/>
-    <mergeCell ref="A439:C439"/>
-    <mergeCell ref="A483:C483"/>
-    <mergeCell ref="A518:C518"/>
-    <mergeCell ref="A278:C278"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A271:C271"/>
-    <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A183:C183"/>
-    <mergeCell ref="A1259:C1259"/>
-    <mergeCell ref="A1288:C1288"/>
-    <mergeCell ref="A1339:C1339"/>
-    <mergeCell ref="A1365:C1365"/>
-    <mergeCell ref="A1400:C1400"/>
+    <mergeCell ref="A1559:C1559"/>
+    <mergeCell ref="A1576:C1576"/>
+    <mergeCell ref="A1625:C1625"/>
+    <mergeCell ref="A1647:C1647"/>
+    <mergeCell ref="A1432:C1432"/>
+    <mergeCell ref="A1460:C1460"/>
+    <mergeCell ref="A1477:C1477"/>
+    <mergeCell ref="A1492:C1492"/>
+    <mergeCell ref="A1525:C1525"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
